--- a/dados/dClientes.xlsx
+++ b/dados/dClientes.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Correia</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38.065.192/0001-97</t>
+          <t>03.594.168/0001-60</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>44799</v>
+        <v>43293</v>
       </c>
     </row>
     <row r="3">
@@ -512,7 +512,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aragão Mendes Ltda.</t>
+          <t>da Mota</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>05.623.798/0001-41</t>
+          <t>57.819.623/0001-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>44302</v>
+        <v>43113</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rodrigues</t>
+          <t>Cavalcanti</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.286.093/0001-65</t>
+          <t>18.907.635/0001-32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>43367</v>
+        <v>44573</v>
       </c>
     </row>
     <row r="5">
@@ -582,7 +582,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pacheco</t>
+          <t>Leão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.532.098/0001-20</t>
+          <t>93.487.210/0001-37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>43963</v>
+        <v>44791</v>
       </c>
     </row>
     <row r="6">
@@ -617,7 +617,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Barros</t>
+          <t>da Cruz Moreira S/A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>87.041.923/0001-70</t>
+          <t>54.376.890/0001-60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>44103</v>
+        <v>44625</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Teixeira Fernandes S.A.</t>
+          <t>Albuquerque</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>04.581.769/0001-00</t>
+          <t>32.048.619/0001-62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>43936</v>
+        <v>44380</v>
       </c>
     </row>
     <row r="8">
@@ -687,7 +687,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Casa Grande - ME</t>
+          <t>Lima Campos e Filhos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>82.539.071/0001-21</t>
+          <t>05.712.649/0001-59</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>44140</v>
+        <v>43982</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nogueira</t>
+          <t>Aragão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>91.065.347/0001-78</t>
+          <t>46.193.280/0001-00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>43292</v>
+        <v>43188</v>
       </c>
     </row>
     <row r="10">
@@ -757,7 +757,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>da Paz</t>
+          <t>Câmara</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>78.345.621/0001-02</t>
+          <t>06.239.154/0001-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>43572</v>
+        <v>43489</v>
       </c>
     </row>
     <row r="11">
@@ -792,7 +792,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Teixeira</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>68.103.475/0001-47</t>
+          <t>62.174.930/0001-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>43785</v>
+        <v>44109</v>
       </c>
     </row>
     <row r="12">
@@ -827,7 +827,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caldeira Sousa e Filhos</t>
+          <t>Freitas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.246.389/0001-28</t>
+          <t>37.968.215/0001-00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>44479</v>
+        <v>44037</v>
       </c>
     </row>
     <row r="13">
@@ -862,7 +862,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Duarte das Neves S.A.</t>
+          <t>da Costa Sá Ltda.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>03.695.741/0001-22</t>
+          <t>13.674.892/0001-58</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>43834</v>
+        <v>44677</v>
       </c>
     </row>
     <row r="14">
@@ -897,7 +897,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Leão S.A.</t>
+          <t>Costela</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30.198.752/0001-70</t>
+          <t>64.309.872/0001-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>43465</v>
+        <v>43485</v>
       </c>
     </row>
     <row r="15">
@@ -932,7 +932,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fonseca e Filhos</t>
+          <t>Vieira Machado Ltda.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>67.823.049/0001-15</t>
+          <t>36.759.081/0001-55</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>43723</v>
+        <v>43485</v>
       </c>
     </row>
     <row r="16">
@@ -967,7 +967,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Teixeira</t>
+          <t>Rocha Freitas Ltda.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.582.436/0001-64</t>
+          <t>54.062.138/0001-44</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>43740</v>
+        <v>44903</v>
       </c>
     </row>
     <row r="17">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mendes das Neves S.A.</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.753.648/0001-92</t>
+          <t>86.032.417/0001-51</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>43869</v>
+        <v>44018</v>
       </c>
     </row>
     <row r="18">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ribeiro</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>80.936.174/0001-08</t>
+          <t>01.423.769/0001-85</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>44513</v>
+        <v>44387</v>
       </c>
     </row>
     <row r="19">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cirino - ME</t>
+          <t>Borges S/A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>04.328.765/0001-06</t>
+          <t>31.628.547/0001-60</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>44665</v>
+        <v>44374</v>
       </c>
     </row>
     <row r="20">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Silva</t>
+          <t>Almeida</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>56.287.304/0001-36</t>
+          <t>59.326.087/0001-34</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44191</v>
+        <v>43951</v>
       </c>
     </row>
     <row r="21">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Campos Monteiro e Filhos</t>
+          <t>da Cunha</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>79.403.825/0001-07</t>
+          <t>48.916.573/0001-96</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43720</v>
+        <v>43534</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pastor</t>
+          <t>da Rocha</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18.469.032/0001-04</t>
+          <t>07.254.139/0001-00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>44893</v>
+        <v>44906</v>
       </c>
     </row>
     <row r="23">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Costa</t>
+          <t>Cavalcanti</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>35.920.471/0001-00</t>
+          <t>23.187.496/0001-50</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>44837</v>
+        <v>43412</v>
       </c>
     </row>
     <row r="24">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jesus</t>
+          <t>Porto Nunes S/A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.329.618/0001-38</t>
+          <t>36.025.497/0001-40</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>44519</v>
+        <v>44263</v>
       </c>
     </row>
     <row r="25">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mendonça</t>
+          <t>da Rosa Ltda.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30.789.615/0001-00</t>
+          <t>79.215.384/0001-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>44724</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="26">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Teixeira</t>
+          <t>Rezende</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27.834.950/0001-78</t>
+          <t>48.715.690/0001-91</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>43613</v>
+        <v>43547</v>
       </c>
     </row>
     <row r="27">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Casa Grande</t>
+          <t>da Luz - EI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23.914.076/0001-28</t>
+          <t>87.902.356/0001-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>44319</v>
+        <v>44116</v>
       </c>
     </row>
     <row r="28">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jesus Silva Ltda.</t>
+          <t>Cassiano</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>93.751.406/0001-97</t>
+          <t>91.254.687/0001-47</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>44701</v>
+        <v>43586</v>
       </c>
     </row>
     <row r="29">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Machado Fernandes - ME</t>
+          <t>Moraes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>35.091.748/0001-21</t>
+          <t>94.832.501/0001-88</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>44324</v>
+        <v>43856</v>
       </c>
     </row>
     <row r="30">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Novais - EI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>08.326.495/0001-55</t>
+          <t>30.624.751/0001-40</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>44583</v>
+        <v>44267</v>
       </c>
     </row>
     <row r="31">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cavalcanti</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16.482.703/0001-33</t>
+          <t>89.426.071/0001-64</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>43128</v>
+        <v>43814</v>
       </c>
     </row>
     <row r="32">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Nascimento S.A.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>50.472.386/0001-02</t>
+          <t>86.312.579/0001-43</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>44168</v>
+        <v>43444</v>
       </c>
     </row>
     <row r="33">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>da Costa Gonçalves - EI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>01.873.265/0001-67</t>
+          <t>20.651.973/0001-06</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>43364</v>
+        <v>43862</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>da Luz Costa S/A</t>
+          <t>Macedo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20.916.478/0001-73</t>
+          <t>06.879.215/0001-00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>43390</v>
+        <v>43615</v>
       </c>
     </row>
     <row r="35">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Moraes S.A.</t>
+          <t>Mendes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>08.913.572/0001-73</t>
+          <t>50.876.329/0001-99</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>43492</v>
+        <v>44214</v>
       </c>
     </row>
     <row r="36">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Melo - EI</t>
+          <t>Andrade Pires S/A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>97.810.456/0001-59</t>
+          <t>46.925.870/0001-72</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>44175</v>
+        <v>44548</v>
       </c>
     </row>
     <row r="37">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Borges</t>
+          <t>Cavalcanti Sampaio Ltda.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>98.563.740/0001-30</t>
+          <t>67.134.982/0001-85</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>43433</v>
+        <v>43718</v>
       </c>
     </row>
     <row r="38">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>da Rocha Dias S/A</t>
+          <t>da Conceição da Mata S.A.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>64.857.291/0001-11</t>
+          <t>49.065.273/0001-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>43209</v>
+        <v>43735</v>
       </c>
     </row>
     <row r="39">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>da Costa</t>
+          <t>Vasconcelos Ltda.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>85.094.631/0001-70</t>
+          <t>53.910.247/0001-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>44635</v>
+        <v>43195</v>
       </c>
     </row>
     <row r="40">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>da Luz - EI</t>
+          <t>Monteiro - ME</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>36.081.952/0001-24</t>
+          <t>54.832.971/0001-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>43518</v>
+        <v>43372</v>
       </c>
     </row>
     <row r="41">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>da Conceição</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>64.198.235/0001-12</t>
+          <t>38.017.526/0001-57</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>43526</v>
+        <v>43472</v>
       </c>
     </row>
     <row r="42">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Montenegro Ltda.</t>
+          <t>Rios</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>43.209.861/0001-97</t>
+          <t>37.894.560/0001-47</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>43775</v>
+        <v>43218</v>
       </c>
     </row>
     <row r="43">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Moreira S.A.</t>
+          <t>Freitas Cassiano Ltda.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>61.349.872/0001-54</t>
+          <t>91.607.352/0001-65</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>44238</v>
+        <v>43688</v>
       </c>
     </row>
     <row r="44">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Correia</t>
+          <t>Fernandes - EI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>34.719.865/0001-24</t>
+          <t>61.032.845/0001-53</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>43451</v>
+        <v>44299</v>
       </c>
     </row>
     <row r="45">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cavalcanti Moura Ltda.</t>
+          <t>Alves S/A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>34.591.206/0001-55</t>
+          <t>29.460.573/0001-80</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>44720</v>
+        <v>44406</v>
       </c>
     </row>
     <row r="46">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>da Costa</t>
+          <t>Moura Ferreira S/A</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>92.035.417/0001-08</t>
+          <t>29.781.604/0001-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>43690</v>
+        <v>43381</v>
       </c>
     </row>
     <row r="47">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ribeiro e Filhos</t>
+          <t>Cavalcante - ME</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>93.852.476/0001-31</t>
+          <t>59.467.018/0001-40</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>44117</v>
+        <v>44732</v>
       </c>
     </row>
     <row r="48">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Araújo e Filhos</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>46.925.730/0001-02</t>
+          <t>28.156.473/0001-00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>44563</v>
+        <v>43637</v>
       </c>
     </row>
     <row r="49">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Souza S.A.</t>
+          <t>Mendes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.584.026/0001-52</t>
+          <t>59.614.708/0001-85</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>44530</v>
+        <v>44096</v>
       </c>
     </row>
     <row r="50">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ferreira Rios e Filhos</t>
+          <t>da Mata e Filhos</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>91.576.342/0001-00</t>
+          <t>67.248.359/0001-53</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>43168</v>
+        <v>44831</v>
       </c>
     </row>
     <row r="51">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Moura e Filhos</t>
+          <t>Monteiro - EI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>56.874.902/0001-01</t>
+          <t>71.350.286/0001-83</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>44659</v>
+        <v>43895</v>
       </c>
     </row>
     <row r="52">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nogueira Marques e Filhos</t>
+          <t>Pimenta</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>59.810.436/0001-99</t>
+          <t>62.409.378/0001-09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>43863</v>
+        <v>43161</v>
       </c>
     </row>
     <row r="53">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Macedo e Filhos</t>
+          <t>Câmara Mendonça e Filhos</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>43.519.706/0001-77</t>
+          <t>20.734.851/0001-75</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>43432</v>
+        <v>44560</v>
       </c>
     </row>
     <row r="54">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Martins S.A.</t>
+          <t>Brito e Filhos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>49.386.107/0001-09</t>
+          <t>74.021.638/0001-45</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>43809</v>
+        <v>44130</v>
       </c>
     </row>
     <row r="55">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Macedo Camargo Ltda.</t>
+          <t>Oliveira</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>63.487.502/0001-09</t>
+          <t>20.945.316/0001-63</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>44330</v>
+        <v>44902</v>
       </c>
     </row>
     <row r="56">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Porto Almeida S.A.</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>21.064.578/0001-81</t>
+          <t>58.367.291/0001-30</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>44877</v>
+        <v>44743</v>
       </c>
     </row>
     <row r="57">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vasconcelos - ME</t>
+          <t>Macedo - EI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>34.691.527/0001-21</t>
+          <t>83.172.954/0001-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>43253</v>
+        <v>43744</v>
       </c>
     </row>
     <row r="58">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pires</t>
+          <t>Araújo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>69.431.705/0001-60</t>
+          <t>39.160.574/0001-62</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>43397</v>
+        <v>44683</v>
       </c>
     </row>
     <row r="59">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Marques</t>
+          <t>Mendonça</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>52.647.108/0001-74</t>
+          <t>52.390.614/0001-20</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>44484</v>
+        <v>43702</v>
       </c>
     </row>
     <row r="60">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Novaes Lima - EI</t>
+          <t>Camargo S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>56.201.984/0001-23</t>
+          <t>27.094.381/0001-71</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>43740</v>
+        <v>44581</v>
       </c>
     </row>
     <row r="61">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Vieira</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>27.095.314/0001-71</t>
+          <t>37.491.208/0001-60</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>43173</v>
+        <v>43679</v>
       </c>
     </row>
     <row r="62">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>da Conceição Pires e Filhos</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>02.968.415/0001-89</t>
+          <t>98.453.270/0001-52</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>43818</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="63">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Oliveira - EI</t>
+          <t>Vasconcelos</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>75.682.904/0001-43</t>
+          <t>52.793.641/0001-44</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>43456</v>
+        <v>44236</v>
       </c>
     </row>
     <row r="64">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Guerra - ME</t>
+          <t>Andrade Ltda.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>86.243.059/0001-26</t>
+          <t>61.375.024/0001-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>44856</v>
+        <v>43695</v>
       </c>
     </row>
     <row r="65">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Siqueira Aragão - ME</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>84.152.370/0001-34</t>
+          <t>52.413.086/0001-88</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>43712</v>
+        <v>44175</v>
       </c>
     </row>
     <row r="66">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Teixeira Araújo Ltda.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>34.916.250/0001-98</t>
+          <t>69.710.843/0001-88</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>44040</v>
+        <v>44023</v>
       </c>
     </row>
     <row r="67">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>78.243.156/0001-90</t>
+          <t>02.841.796/0001-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>44042</v>
+        <v>43259</v>
       </c>
     </row>
     <row r="68">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pastor</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>50.739.286/0001-08</t>
+          <t>67.429.580/0001-08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>43901</v>
+        <v>44703</v>
       </c>
     </row>
     <row r="69">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Guerra</t>
+          <t>Andrade</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>78.053.124/0001-22</t>
+          <t>54.768.129/0001-73</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>43947</v>
+        <v>44744</v>
       </c>
     </row>
     <row r="70">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>da Paz</t>
+          <t>Lopes</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10.243.958/0001-67</t>
+          <t>45.708.196/0001-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>44768</v>
+        <v>44019</v>
       </c>
     </row>
     <row r="71">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rezende</t>
+          <t>Sá</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>45.781.239/0001-84</t>
+          <t>86.094.721/0001-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>43934</v>
+        <v>43744</v>
       </c>
     </row>
     <row r="72">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ramos e Filhos</t>
+          <t>da Rocha</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>46.312.750/0001-08</t>
+          <t>34.502.187/0001-43</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>43725</v>
+        <v>44492</v>
       </c>
     </row>
     <row r="73">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ribeiro Dias S/A</t>
+          <t>Siqueira</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>80.957.426/0001-77</t>
+          <t>95.820.163/0001-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>43499</v>
+        <v>44748</v>
       </c>
     </row>
     <row r="74">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cavalcanti e Filhos</t>
+          <t>da Cunha</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>02.963.475/0001-09</t>
+          <t>07.342.869/0001-63</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>43881</v>
+        <v>44758</v>
       </c>
     </row>
     <row r="75">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fogaça</t>
+          <t>Siqueira</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>08.723.946/0001-98</t>
+          <t>04.759.261/0001-40</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>43628</v>
+        <v>44659</v>
       </c>
     </row>
     <row r="76">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vasconcelos Pastor S.A.</t>
+          <t>Cavalcante</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>78.195.024/0001-30</t>
+          <t>31.845.260/0001-91</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>44634</v>
+        <v>43657</v>
       </c>
     </row>
     <row r="77">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alves</t>
+          <t>Campos Campos S/A</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10.796.825/0001-18</t>
+          <t>16.950.243/0001-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>44653</v>
+        <v>43806</v>
       </c>
     </row>
     <row r="78">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Camargo</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>65.092.781/0001-37</t>
+          <t>01.849.263/0001-32</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>44457</v>
+        <v>44770</v>
       </c>
     </row>
     <row r="79">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Araújo</t>
+          <t>Viana Pires e Filhos</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>69.015.827/0001-75</t>
+          <t>23.945.807/0001-00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>44268</v>
+        <v>44070</v>
       </c>
     </row>
     <row r="80">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pimenta</t>
+          <t>da Cunha - EI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>47.586.039/0001-04</t>
+          <t>78.634.192/0001-85</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>44667</v>
+        <v>43767</v>
       </c>
     </row>
     <row r="81">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Ferreira</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>63.427.851/0001-35</t>
+          <t>54.709.163/0001-77</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>44682</v>
+        <v>43293</v>
       </c>
     </row>
     <row r="82">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>da Paz Mendonça - ME</t>
+          <t>Macedo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>51.374.906/0001-07</t>
+          <t>12.087.953/0001-18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>44759</v>
+        <v>44336</v>
       </c>
     </row>
     <row r="83">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Novaes S/A</t>
+          <t>Jesus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>85.791.064/0001-00</t>
+          <t>58.120.473/0001-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>44415</v>
+        <v>43108</v>
       </c>
     </row>
     <row r="84">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ferreira Novaes - ME</t>
+          <t>da Paz</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20.793.416/0001-11</t>
+          <t>25.798.064/0001-00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>44382</v>
+        <v>43524</v>
       </c>
     </row>
     <row r="85">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Moreira</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>45.321.890/0001-71</t>
+          <t>68.012.543/0001-62</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>44356</v>
+        <v>43604</v>
       </c>
     </row>
     <row r="86">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ferreira</t>
+          <t>Teixeira - ME</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>63.742.810/0001-33</t>
+          <t>90.584.637/0001-65</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>43458</v>
+        <v>44330</v>
       </c>
     </row>
     <row r="87">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lopes Cardoso S/A</t>
+          <t>Campos Ltda.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>85.409.237/0001-83</t>
+          <t>81.275.463/0001-68</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>44456</v>
+        <v>43525</v>
       </c>
     </row>
     <row r="88">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Farias</t>
+          <t>Sales Moraes S/A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>41.596.730/0001-84</t>
+          <t>49.872.165/0001-42</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>43107</v>
+        <v>44071</v>
       </c>
     </row>
     <row r="89">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pimenta</t>
+          <t>das Neves</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>94.385.107/0001-49</t>
+          <t>75.120.493/0001-00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>43184</v>
+        <v>44831</v>
       </c>
     </row>
     <row r="90">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Carvalho S/A</t>
+          <t>Azevedo - EI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>76.524.831/0001-24</t>
+          <t>17.826.049/0001-09</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>43971</v>
+        <v>44004</v>
       </c>
     </row>
     <row r="91">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Campos</t>
+          <t>Sá</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>50.146.398/0001-47</t>
+          <t>03.761.824/0001-72</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>43594</v>
+        <v>44016</v>
       </c>
     </row>
     <row r="92">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Garcia Sales Ltda.</t>
+          <t>Guerra Pereira Ltda.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>74.651.203/0001-84</t>
+          <t>20.547.893/0001-05</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>43867</v>
+        <v>43456</v>
       </c>
     </row>
     <row r="93">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Freitas</t>
+          <t>Silva</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>62.397.508/0001-22</t>
+          <t>59.613.824/0001-80</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>43865</v>
+        <v>43718</v>
       </c>
     </row>
     <row r="94">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cassiano</t>
+          <t>Pastor Albuquerque e Filhos</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>85.792.630/0001-07</t>
+          <t>72.934.681/0001-76</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>43277</v>
+        <v>43187</v>
       </c>
     </row>
     <row r="95">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>da Conceição</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>18.742.695/0001-42</t>
+          <t>71.392.860/0001-66</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>43297</v>
+        <v>43274</v>
       </c>
     </row>
     <row r="96">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alves Gomes S.A.</t>
+          <t>Ribeiro</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>06.483.251/0001-50</t>
+          <t>81.723.609/0001-90</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>43140</v>
+        <v>44539</v>
       </c>
     </row>
     <row r="97">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Carvalho e Filhos</t>
+          <t>Lima da Paz - EI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>70.368.425/0001-33</t>
+          <t>16.385.790/0001-00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>43964</v>
+        <v>44150</v>
       </c>
     </row>
     <row r="98">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Teixeira - EI</t>
+          <t>Costela</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>69.074.823/0001-68</t>
+          <t>45.680.731/0001-63</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>44914</v>
+        <v>43649</v>
       </c>
     </row>
     <row r="99">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Moura Abreu - ME</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>39.617.402/0001-75</t>
+          <t>81.924.536/0001-03</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>44669</v>
+        <v>44562</v>
       </c>
     </row>
     <row r="100">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Vasconcelos S.A.</t>
+          <t>da Mata</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>51.647.293/0001-34</t>
+          <t>13.690.428/0001-55</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>44868</v>
+        <v>44663</v>
       </c>
     </row>
     <row r="101">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cunha Vieira - EI</t>
+          <t>Pastor</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>41.962.053/0001-70</t>
+          <t>36.107.842/0001-94</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>44702</v>
+        <v>44120</v>
       </c>
     </row>
     <row r="102">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>das Neves - EI</t>
+          <t>da Rosa - EI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>64.103.257/0001-51</t>
+          <t>30.491.765/0001-32</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>44789</v>
+        <v>43657</v>
       </c>
     </row>
     <row r="103">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>da Mata</t>
+          <t>Mendes</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>26.814.507/0001-72</t>
+          <t>81.023.456/0001-79</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>44428</v>
+        <v>43541</v>
       </c>
     </row>
     <row r="104">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sá S/A</t>
+          <t>Pimenta S/A</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>53.164.280/0001-30</t>
+          <t>78.610.495/0001-68</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>44897</v>
+        <v>44543</v>
       </c>
     </row>
     <row r="105">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>da Rosa Ribeiro S.A.</t>
+          <t>Siqueira Oliveira S/A</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>09.781.326/0001-78</t>
+          <t>89.754.026/0001-39</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>43256</v>
+        <v>44285</v>
       </c>
     </row>
     <row r="106">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Peixoto</t>
+          <t>Machado</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>94.183.526/0001-06</t>
+          <t>03.286.947/0001-07</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>44652</v>
+        <v>44108</v>
       </c>
     </row>
     <row r="107">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Machado</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>67.239.845/0001-05</t>
+          <t>10.974.258/0001-42</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>43842</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="108">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Almeida - ME</t>
+          <t>da Cruz S/A</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>86.075.341/0001-41</t>
+          <t>38.145.026/0001-09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>43396</v>
+        <v>43252</v>
       </c>
     </row>
     <row r="109">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Melo Araújo - ME</t>
+          <t>Barbosa Dias - EI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>19.780.642/0001-89</t>
+          <t>26.098.153/0001-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>43117</v>
+        <v>44804</v>
       </c>
     </row>
     <row r="110">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Siqueira - EI</t>
+          <t>Teixeira S.A.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>23.761.948/0001-65</t>
+          <t>09.735.684/0001-44</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>43739</v>
+        <v>43250</v>
       </c>
     </row>
     <row r="111">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cunha</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>94.701.325/0001-45</t>
+          <t>27.908.156/0001-21</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>44475</v>
+        <v>44754</v>
       </c>
     </row>
     <row r="112">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Duarte Barros - ME</t>
+          <t>Oliveira</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>19.465.072/0001-32</t>
+          <t>57.102.684/0001-50</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>43120</v>
+        <v>43992</v>
       </c>
     </row>
     <row r="113">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cavalcanti</t>
+          <t>Pires - EI</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>34.985.612/0001-00</t>
+          <t>10.762.843/0001-89</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>44000</v>
+        <v>43611</v>
       </c>
     </row>
     <row r="114">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Oliveira</t>
+          <t>Pastor Ltda.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>60.982.143/0001-78</t>
+          <t>08.963.712/0001-18</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>44164</v>
+        <v>43853</v>
       </c>
     </row>
     <row r="115">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ribeiro e Filhos</t>
+          <t>Sales Brito S/A</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>59.638.701/0001-01</t>
+          <t>70.645.391/0001-87</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>44332</v>
+        <v>44817</v>
       </c>
     </row>
     <row r="116">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>das Neves e Filhos</t>
+          <t>Farias S/A</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>34.698.127/0001-48</t>
+          <t>60.453.219/0001-78</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>43548</v>
+        <v>43210</v>
       </c>
     </row>
     <row r="117">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cavalcanti Pimenta Ltda.</t>
+          <t>Borges Borges S.A.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>32.658.710/0001-08</t>
+          <t>01.974.365/0001-80</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>44176</v>
+        <v>44597</v>
       </c>
     </row>
     <row r="118">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Oliveira</t>
+          <t>Cardoso</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>58.341.960/0001-03</t>
+          <t>83.427.601/0001-02</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>44238</v>
+        <v>43551</v>
       </c>
     </row>
     <row r="119">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>da Costa</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>67.140.938/0001-88</t>
+          <t>69.104.837/0001-87</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>43777</v>
+        <v>43359</v>
       </c>
     </row>
     <row r="120">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Guerra</t>
+          <t>Silva Andrade e Filhos</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>47.628.039/0001-11</t>
+          <t>38.264.091/0001-45</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>43928</v>
+        <v>44323</v>
       </c>
     </row>
     <row r="121">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pires Cassiano S/A</t>
+          <t>Viana - EI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>40.297.861/0001-06</t>
+          <t>31.746.205/0001-44</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>43528</v>
+        <v>44668</v>
       </c>
     </row>
     <row r="122">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Correia Brito S/A</t>
+          <t>Porto Campos S.A.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>75.201.849/0001-22</t>
+          <t>75.620.948/0001-49</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>43976</v>
+        <v>43129</v>
       </c>
     </row>
     <row r="123">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Moura</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>43.718.956/0001-36</t>
+          <t>37.528.169/0001-29</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>43523</v>
+        <v>43250</v>
       </c>
     </row>
     <row r="124">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Almeida</t>
+          <t>Araújo Ltda.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>10.985.362/0001-32</t>
+          <t>35.170.482/0001-02</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>43130</v>
+        <v>44152</v>
       </c>
     </row>
     <row r="125">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cavalcante Ltda.</t>
+          <t>Machado Mendes S.A.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>95.460.713/0001-44</t>
+          <t>82.910.543/0001-00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>43611</v>
+        <v>43785</v>
       </c>
     </row>
     <row r="126">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vieira</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>12.345.970/0001-08</t>
+          <t>60.129.875/0001-10</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>44676</v>
+        <v>43878</v>
       </c>
     </row>
     <row r="127">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>da Mata</t>
+          <t>Mendonça S/A</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>38.504.617/0001-17</t>
+          <t>26.941.385/0001-85</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>44899</v>
+        <v>44705</v>
       </c>
     </row>
     <row r="128">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lima Alves S.A.</t>
+          <t>Garcia - EI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>62.937.854/0001-56</t>
+          <t>15.063.829/0001-00</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>43829</v>
+        <v>44472</v>
       </c>
     </row>
     <row r="129">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Correia S/A</t>
+          <t>Pereira Nascimento e Filhos</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>51.647.983/0001-93</t>
+          <t>94.673.280/0001-42</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>43960</v>
+        <v>44475</v>
       </c>
     </row>
     <row r="130">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ramos S.A.</t>
+          <t>Guerra Martins Ltda.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>70.254.619/0001-08</t>
+          <t>73.014.592/0001-74</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>44443</v>
+        <v>43166</v>
       </c>
     </row>
     <row r="131">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Borges</t>
+          <t>da Rocha S.A.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>72.143.698/0001-05</t>
+          <t>13.762.490/0001-05</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>43442</v>
+        <v>43485</v>
       </c>
     </row>
     <row r="132">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jesus - ME</t>
+          <t>da Rosa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>29.053.864/0001-53</t>
+          <t>41.635.708/0001-04</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>43869</v>
+        <v>44757</v>
       </c>
     </row>
     <row r="133">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Guerra</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>05.372.816/0001-60</t>
+          <t>53.248.179/0001-67</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>43399</v>
+        <v>44859</v>
       </c>
     </row>
     <row r="134">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Castro e Filhos</t>
+          <t>Rodrigues</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>45.819.302/0001-24</t>
+          <t>63.289.701/0001-02</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>43101</v>
+        <v>44153</v>
       </c>
     </row>
     <row r="135">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mendes S/A</t>
+          <t>Castro e Filhos</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>82.394.570/0001-78</t>
+          <t>02.561.489/0001-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>44119</v>
+        <v>43417</v>
       </c>
     </row>
     <row r="136">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Fonseca e Filhos</t>
+          <t>Araújo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>97.834.210/0001-17</t>
+          <t>81.043.792/0001-83</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>43148</v>
+        <v>43587</v>
       </c>
     </row>
     <row r="137">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Barbosa - EI</t>
+          <t>Mendonça da Costa e Filhos</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>89.650.372/0001-77</t>
+          <t>98.350.647/0001-48</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>43232</v>
+        <v>44413</v>
       </c>
     </row>
     <row r="138">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Pimenta Albuquerque Ltda.</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>81.523.967/0001-50</t>
+          <t>85.729.064/0001-80</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>44092</v>
+        <v>43732</v>
       </c>
     </row>
     <row r="139">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>da Cruz - ME</t>
+          <t>Ferreira</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>60.157.382/0001-93</t>
+          <t>61.905.483/0001-68</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>43642</v>
+        <v>43671</v>
       </c>
     </row>
     <row r="140">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Moreira Leão e Filhos</t>
+          <t>Alves</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>65.712.094/0001-77</t>
+          <t>21.593.876/0001-69</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>44072</v>
+        <v>44839</v>
       </c>
     </row>
     <row r="141">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Marques Ramos - ME</t>
+          <t>Guerra Novais e Filhos</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>63.097.458/0001-20</t>
+          <t>79.843.265/0001-01</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>43316</v>
+        <v>43144</v>
       </c>
     </row>
     <row r="142">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Siqueira</t>
+          <t>Cassiano</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>76.428.059/0001-47</t>
+          <t>37.802.619/0001-20</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>43102</v>
+        <v>44397</v>
       </c>
     </row>
     <row r="143">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cavalcanti S.A.</t>
+          <t>Gonçalves - ME</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>36.218.579/0001-00</t>
+          <t>62.584.039/0001-50</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>44586</v>
+        <v>44401</v>
       </c>
     </row>
     <row r="144">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>da Paz - EI</t>
+          <t>da Luz</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>41.835.970/0001-94</t>
+          <t>70.841.625/0001-61</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>43466</v>
+        <v>43874</v>
       </c>
     </row>
     <row r="145">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Farias</t>
+          <t>Cunha - ME</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>65.902.148/0001-67</t>
+          <t>05.392.716/0001-03</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>44392</v>
+        <v>43823</v>
       </c>
     </row>
     <row r="146">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Nunes</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>42.709.835/0001-65</t>
+          <t>89.416.732/0001-70</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>44196</v>
+        <v>43227</v>
       </c>
     </row>
     <row r="147">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Vasconcelos</t>
+          <t>Leão Pacheco e Filhos</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>40.356.987/0001-04</t>
+          <t>52.647.089/0001-86</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>44381</v>
+        <v>43692</v>
       </c>
     </row>
     <row r="148">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>das Neves</t>
+          <t>Nunes</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>73.619.058/0001-91</t>
+          <t>31.726.508/0001-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>44236</v>
+        <v>44299</v>
       </c>
     </row>
     <row r="149">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cavalcante da Conceição Ltda.</t>
+          <t>Campos</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>41.930.652/0001-02</t>
+          <t>05.638.924/0001-31</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>44180</v>
+        <v>44265</v>
       </c>
     </row>
     <row r="150">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Costela</t>
+          <t>Melo - ME</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>12.936.540/0001-60</t>
+          <t>21.486.059/0001-01</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>44473</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="151">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rodrigues</t>
+          <t>da Cruz S/A</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>85.102.967/0001-37</t>
+          <t>61.052.748/0001-22</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>44549</v>
+        <v>44427</v>
       </c>
     </row>
     <row r="152">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>da Conceição</t>
+          <t>Sousa Rocha S.A.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>65.374.198/0001-19</t>
+          <t>86.724.095/0001-01</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>43435</v>
+        <v>43987</v>
       </c>
     </row>
     <row r="153">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Fonseca Machado e Filhos</t>
+          <t>da Rosa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>83.514.620/0001-76</t>
+          <t>07.842.596/0001-16</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>43339</v>
+        <v>43655</v>
       </c>
     </row>
     <row r="154">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Farias</t>
+          <t>Fernandes Cavalcanti e Filhos</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>40.839.621/0001-88</t>
+          <t>76.435.819/0001-43</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>43911</v>
+        <v>43170</v>
       </c>
     </row>
     <row r="155">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ribeiro - EI</t>
+          <t>Câmara</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>79.306.581/0001-44</t>
+          <t>62.905.741/0001-79</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>44662</v>
+        <v>43473</v>
       </c>
     </row>
     <row r="156">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>das Neves Camargo S/A</t>
+          <t>Melo</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>38.710.425/0001-67</t>
+          <t>94.632.751/0001-74</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>44488</v>
+        <v>43745</v>
       </c>
     </row>
     <row r="157">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nascimento e Filhos</t>
+          <t>Pacheco</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>24.693.075/0001-63</t>
+          <t>07.421.653/0001-93</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>43773</v>
+        <v>43226</v>
       </c>
     </row>
     <row r="158">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Abreu Melo S/A</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>57.391.862/0001-00</t>
+          <t>49.732.568/0001-96</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>43243</v>
+        <v>43335</v>
       </c>
     </row>
     <row r="159">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lopes Leão S/A</t>
+          <t>Fogaça Souza e Filhos</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>83.756.219/0001-42</t>
+          <t>71.506.298/0001-54</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>44698</v>
+        <v>43104</v>
       </c>
     </row>
     <row r="160">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Sampaio - ME</t>
+          <t>Melo S/A</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>83.410.972/0001-81</t>
+          <t>42.609.831/0001-05</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>43894</v>
+        <v>43478</v>
       </c>
     </row>
     <row r="161">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Marques e Filhos</t>
+          <t>Correia Costela Ltda.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>64.250.139/0001-76</t>
+          <t>79.213.580/0001-55</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>43607</v>
+        <v>44391</v>
       </c>
     </row>
     <row r="162">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Costela</t>
+          <t>Moura da Rosa - ME</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>19.385.072/0001-22</t>
+          <t>69.782.034/0001-81</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>44193</v>
+        <v>44392</v>
       </c>
     </row>
     <row r="163">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>da Cruz - EI</t>
+          <t>Ribeiro e Filhos</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>83.540.796/0001-00</t>
+          <t>95.842.603/0001-47</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>44833</v>
+        <v>43345</v>
       </c>
     </row>
     <row r="164">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mendonça - ME</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>73.251.968/0001-64</t>
+          <t>80.935.674/0001-17</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>44072</v>
+        <v>44661</v>
       </c>
     </row>
     <row r="165">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mendonça Gonçalves Ltda.</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>17.380.592/0001-17</t>
+          <t>90.312.584/0001-23</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>44202</v>
+        <v>44537</v>
       </c>
     </row>
     <row r="166">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Novais S/A</t>
+          <t>Melo</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10.473.526/0001-42</t>
+          <t>06.348.251/0001-48</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>44355</v>
+        <v>43727</v>
       </c>
     </row>
     <row r="167">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Cavalcanti</t>
+          <t>Rezende Aparecida e Filhos</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>56.843.790/0001-21</t>
+          <t>98.034.216/0001-72</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>44354</v>
+        <v>43305</v>
       </c>
     </row>
     <row r="168">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Caldeira Ltda.</t>
+          <t>Abreu da Costa Ltda.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10.857.396/0001-41</t>
+          <t>73.405.296/0001-02</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>43238</v>
+        <v>43442</v>
       </c>
     </row>
     <row r="169">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Siqueira S/A</t>
+          <t>Vargas Sales - ME</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>96.127.084/0001-06</t>
+          <t>68.912.437/0001-35</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>43663</v>
+        <v>44854</v>
       </c>
     </row>
     <row r="170">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>da Conceição Pimenta S.A.</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>40.718.659/0001-00</t>
+          <t>36.274.810/0001-83</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>44816</v>
+        <v>43304</v>
       </c>
     </row>
     <row r="171">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>das Neves</t>
+          <t>Campos Aparecida e Filhos</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>64.291.037/0001-07</t>
+          <t>23.706.594/0001-56</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>43848</v>
+        <v>43124</v>
       </c>
     </row>
     <row r="172">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Fonseca e Filhos</t>
+          <t>Nogueira e Filhos</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>48.209.657/0001-90</t>
+          <t>92.734.816/0001-67</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>43936</v>
+        <v>44881</v>
       </c>
     </row>
     <row r="173">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Fernandes - ME</t>
+          <t>Caldeira S.A.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>78.269.501/0001-65</t>
+          <t>62.048.531/0001-01</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>44002</v>
+        <v>44631</v>
       </c>
     </row>
     <row r="174">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>da Mota</t>
+          <t>Mendes Pimenta - EI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>19.205.348/0001-43</t>
+          <t>95.674.031/0001-34</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>44348</v>
+        <v>43655</v>
       </c>
     </row>
     <row r="175">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ribeiro</t>
+          <t>Cirino e Filhos</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>45.602.319/0001-25</t>
+          <t>28.479.065/0001-80</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>43540</v>
+        <v>44896</v>
       </c>
     </row>
     <row r="176">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mendonça da Cruz S/A</t>
+          <t>da Rocha</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>40.325.169/0001-36</t>
+          <t>26.350.894/0001-33</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>44315</v>
+        <v>44063</v>
       </c>
     </row>
     <row r="177">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Almeida</t>
+          <t>da Paz</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>85.137.290/0001-72</t>
+          <t>27.068.549/0001-74</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>44907</v>
+        <v>44083</v>
       </c>
     </row>
     <row r="178">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Costa Dias - EI</t>
+          <t>Duarte</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>61.784.925/0001-65</t>
+          <t>04.738.521/0001-00</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>44838</v>
+        <v>43138</v>
       </c>
     </row>
     <row r="179">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Câmara Guerra S.A.</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>67.912.508/0001-37</t>
+          <t>60.723.145/0001-42</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>43783</v>
+        <v>44782</v>
       </c>
     </row>
     <row r="180">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Cassiano</t>
+          <t>Castro Ltda.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>54.679.301/0001-12</t>
+          <t>58.129.647/0001-06</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>43594</v>
+        <v>44857</v>
       </c>
     </row>
     <row r="181">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Freitas S.A.</t>
+          <t>Guerra Nunes - ME</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>30.981.765/0001-10</t>
+          <t>36.097.125/0001-29</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>43621</v>
+        <v>43877</v>
       </c>
     </row>
     <row r="182">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Vieira</t>
+          <t>Fernandes Ltda.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20.495.637/0001-03</t>
+          <t>30.248.175/0001-83</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>44777</v>
+        <v>43582</v>
       </c>
     </row>
     <row r="183">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ramos S/A</t>
+          <t>Leão S.A.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>64.387.295/0001-83</t>
+          <t>56.784.103/0001-44</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>43548</v>
+        <v>43720</v>
       </c>
     </row>
     <row r="184">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Leão e Filhos</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>85.147.932/0001-14</t>
+          <t>83.526.941/0001-90</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>43953</v>
+        <v>44343</v>
       </c>
     </row>
     <row r="185">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Silva da Costa - EI</t>
+          <t>Alves - EI</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>10.854.937/0001-88</t>
+          <t>53.740.682/0001-35</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>44098</v>
+        <v>44901</v>
       </c>
     </row>
     <row r="186">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Duarte</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>18.956.430/0001-47</t>
+          <t>31.678.905/0001-49</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>43777</v>
+        <v>43164</v>
       </c>
     </row>
     <row r="187">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Barros</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>19.580.743/0001-06</t>
+          <t>82.519.764/0001-52</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>43848</v>
+        <v>43635</v>
       </c>
     </row>
     <row r="188">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Porto Castro S.A.</t>
+          <t>Pereira S.A.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>25.109.764/0001-40</t>
+          <t>29.634.708/0001-86</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>44789</v>
+        <v>43840</v>
       </c>
     </row>
     <row r="189">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Teixeira Câmara - ME</t>
+          <t>Leão Silveira Ltda.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>62.580.149/0001-44</t>
+          <t>08.214.769/0001-14</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>43512</v>
+        <v>43702</v>
       </c>
     </row>
     <row r="190">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Peixoto Ltda.</t>
+          <t>Ribeiro</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>97.841.036/0001-30</t>
+          <t>15.308.729/0001-05</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>43750</v>
+        <v>43992</v>
       </c>
     </row>
     <row r="191">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Campos</t>
+          <t>Aragão</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>41.037.965/0001-36</t>
+          <t>31.096.478/0001-90</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>44327</v>
+        <v>43534</v>
       </c>
     </row>
     <row r="192">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>da Mota S.A.</t>
+          <t>Rezende</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>80.675.942/0001-09</t>
+          <t>72.845.160/0001-42</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>43949</v>
+        <v>44022</v>
       </c>
     </row>
     <row r="193">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Porto S/A</t>
+          <t>Duarte e Filhos</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>89.043.621/0001-66</t>
+          <t>81.524.360/0001-94</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>43628</v>
+        <v>44206</v>
       </c>
     </row>
     <row r="194">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Rodrigues Viana e Filhos</t>
+          <t>Cavalcante - EI</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>43.261.075/0001-39</t>
+          <t>95.478.162/0001-46</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>43506</v>
+        <v>44580</v>
       </c>
     </row>
     <row r="195">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Oliveira Ltda.</t>
+          <t>Sousa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>49.813.520/0001-02</t>
+          <t>65.830.912/0001-36</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>43356</v>
+        <v>44537</v>
       </c>
     </row>
     <row r="196">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Pacheco</t>
+          <t>Azevedo</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>93.826.140/0001-02</t>
+          <t>17.032.596/0001-04</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>44178</v>
+        <v>44597</v>
       </c>
     </row>
     <row r="197">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fonseca Carvalho - EI</t>
+          <t>Vasconcelos</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>51.274.038/0001-93</t>
+          <t>69.047.215/0001-64</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>43520</v>
+        <v>44268</v>
       </c>
     </row>
     <row r="198">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Montenegro - EI</t>
+          <t>Andrade da Mata e Filhos</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>37.492.681/0001-62</t>
+          <t>45.738.602/0001-89</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>43876</v>
+        <v>44452</v>
       </c>
     </row>
     <row r="199">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>da Rosa</t>
+          <t>Ferreira - EI</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>26.378.540/0001-05</t>
+          <t>42.680.173/0001-48</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>43315</v>
+        <v>43349</v>
       </c>
     </row>
     <row r="200">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>da Conceição Ltda.</t>
+          <t>Teixeira Oliveira - ME</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>51.670.923/0001-91</t>
+          <t>42.873.651/0001-36</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>44734</v>
+        <v>44043</v>
       </c>
     </row>
     <row r="201">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Viana</t>
+          <t>Moreira Siqueira S.A.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>05.219.638/0001-31</t>
+          <t>69.372.804/0001-18</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>44563</v>
+        <v>43888</v>
       </c>
     </row>
   </sheetData>
